--- a/RACK.xlsx
+++ b/RACK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Downloads\New folder (5)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA38468-6EDF-43D0-8CD7-5D6CAF86BFF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AA79D0-5B15-4056-9B1B-36363B89BE1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ML" sheetId="2" r:id="rId1"/>
@@ -1993,7 +1993,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="214">
+  <cellXfs count="205">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2177,12 +2177,6 @@
     <xf numFmtId="0" fontId="3" fillId="18" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2208,9 +2202,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2253,13 +2244,9 @@
     <xf numFmtId="0" fontId="7" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2270,7 +2257,6 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2286,16 +2272,12 @@
     <xf numFmtId="0" fontId="4" fillId="19" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2309,19 +2291,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2336,24 +2309,117 @@
     <xf numFmtId="0" fontId="9" fillId="20" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="20" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2361,6 +2427,87 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2372,190 +2519,20 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2895,7 +2872,8 @@
   <dimension ref="A1:T13"/>
   <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="11.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="11.5546875" style="2" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" style="2" customWidth="1"/>
     <col min="8" max="14" width="11.5546875" style="2" customWidth="1"/>
     <col min="15" max="15" width="13.77734375" style="2" customWidth="1"/>
@@ -2905,32 +2883,32 @@
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="39"/>
-      <c r="B1" s="150" t="s">
+      <c r="B1" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="152"/>
-      <c r="H1" s="150" t="s">
+      <c r="C1" s="182"/>
+      <c r="D1" s="182"/>
+      <c r="E1" s="182"/>
+      <c r="F1" s="183"/>
+      <c r="H1" s="181" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="152"/>
-      <c r="O1" s="153" t="s">
+      <c r="I1" s="182"/>
+      <c r="J1" s="182"/>
+      <c r="K1" s="182"/>
+      <c r="L1" s="182"/>
+      <c r="M1" s="183"/>
+      <c r="O1" s="184" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="154"/>
-      <c r="Q1" s="154"/>
-      <c r="R1" s="154"/>
-      <c r="S1" s="154"/>
-      <c r="T1" s="155"/>
+      <c r="P1" s="185"/>
+      <c r="Q1" s="185"/>
+      <c r="R1" s="185"/>
+      <c r="S1" s="185"/>
+      <c r="T1" s="186"/>
     </row>
     <row r="2" spans="1:20" s="3" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="162" t="s">
+      <c r="A2" s="193" t="s">
         <v>436</v>
       </c>
       <c r="B2" s="40" t="s">
@@ -2972,7 +2950,7 @@
       <c r="T2" s="62"/>
     </row>
     <row r="3" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="163"/>
+      <c r="A3" s="194"/>
       <c r="B3" s="24"/>
       <c r="C3" s="69"/>
       <c r="D3" s="69"/>
@@ -2998,7 +2976,7 @@
       <c r="T3" s="12"/>
     </row>
     <row r="4" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="164"/>
+      <c r="A4" s="195"/>
       <c r="B4" s="26"/>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
@@ -3042,7 +3020,7 @@
       <c r="T5" s="68"/>
     </row>
     <row r="6" spans="1:20" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="156" t="s">
+      <c r="A6" s="187" t="s">
         <v>437</v>
       </c>
       <c r="B6" s="45" t="s">
@@ -3098,7 +3076,7 @@
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A7" s="157"/>
+      <c r="A7" s="188"/>
       <c r="B7" s="48" t="s">
         <v>150</v>
       </c>
@@ -3150,7 +3128,7 @@
       <c r="T7" s="65"/>
     </row>
     <row r="8" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="158"/>
+      <c r="A8" s="189"/>
       <c r="B8" s="51" t="s">
         <v>166</v>
       </c>
@@ -3222,7 +3200,7 @@
       <c r="T9" s="68"/>
     </row>
     <row r="10" spans="1:20" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="159" t="s">
+      <c r="A10" s="190" t="s">
         <v>438</v>
       </c>
       <c r="B10" s="54" t="s">
@@ -3264,7 +3242,7 @@
       <c r="T10" s="62"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A11" s="160"/>
+      <c r="A11" s="191"/>
       <c r="B11" s="57" t="s">
         <v>191</v>
       </c>
@@ -3302,7 +3280,7 @@
       <c r="T11" s="12"/>
     </row>
     <row r="12" spans="1:20" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="161"/>
+      <c r="A12" s="192"/>
       <c r="B12" s="26"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
@@ -3346,7 +3324,7 @@
   <dimension ref="A1:W16"/>
   <sheetFormatPr defaultColWidth="10.21875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.21875" style="72" customWidth="1"/>
+    <col min="1" max="1" width="6.44140625" style="72" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="11.44140625" style="72" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8" style="72" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="11.33203125" style="72" bestFit="1" customWidth="1"/>
@@ -3359,38 +3337,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="146"/>
-      <c r="H1" s="147" t="s">
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="168"/>
+      <c r="H1" s="196" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="148"/>
-      <c r="J1" s="148"/>
-      <c r="K1" s="148"/>
-      <c r="L1" s="148"/>
-      <c r="M1" s="149"/>
-      <c r="O1" s="144" t="s">
+      <c r="I1" s="197"/>
+      <c r="J1" s="197"/>
+      <c r="K1" s="197"/>
+      <c r="L1" s="197"/>
+      <c r="M1" s="198"/>
+      <c r="O1" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="144" t="s">
+      <c r="P1" s="167"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="167"/>
+      <c r="S1" s="167"/>
+      <c r="T1" s="168"/>
+      <c r="U1" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="145"/>
-      <c r="W1" s="146"/>
+      <c r="V1" s="167"/>
+      <c r="W1" s="168"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="74"/>
-      <c r="B2" s="75" t="s">
+      <c r="A2" s="175" t="s">
+        <v>436</v>
+      </c>
+      <c r="B2" s="73" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="4" t="s">
@@ -3402,80 +3382,78 @@
       <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="76"/>
-      <c r="H2" s="77" t="s">
+      <c r="F2" s="74"/>
+      <c r="H2" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="78" t="s">
+      <c r="I2" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="78" t="s">
+      <c r="J2" s="76" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="78" t="s">
+      <c r="K2" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="78" t="s">
+      <c r="L2" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="79" t="s">
+      <c r="M2" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="O2" s="80" t="s">
+      <c r="O2" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="P2" s="81" t="s">
+      <c r="P2" s="79" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="81" t="s">
+      <c r="Q2" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="R2" s="81" t="s">
+      <c r="R2" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="S2" s="81" t="s">
+      <c r="S2" s="79" t="s">
         <v>18</v>
       </c>
-      <c r="T2" s="82" t="s">
+      <c r="T2" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="76"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="74"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A3" s="84" t="s">
-        <v>436</v>
-      </c>
-      <c r="B3" s="85" t="s">
+      <c r="A3" s="176"/>
+      <c r="B3" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="86" t="s">
+      <c r="C3" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="86" t="s">
+      <c r="D3" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="86" t="s">
+      <c r="E3" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="87"/>
-      <c r="H3" s="88" t="s">
+      <c r="F3" s="84"/>
+      <c r="H3" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="89" t="s">
+      <c r="I3" s="86" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="89" t="s">
+      <c r="J3" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="89" t="s">
+      <c r="K3" s="86" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="89" t="s">
+      <c r="L3" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="90" t="s">
+      <c r="M3" s="87" t="s">
         <v>29</v>
       </c>
       <c r="O3" s="8" t="s">
@@ -3496,12 +3474,12 @@
       <c r="T3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="U3" s="91"/>
-      <c r="V3" s="91"/>
-      <c r="W3" s="87"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="W3" s="84"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" s="84"/>
+      <c r="A4" s="176"/>
       <c r="B4" s="8" t="s">
         <v>36</v>
       </c>
@@ -3512,48 +3490,48 @@
         <v>38</v>
       </c>
       <c r="E4" s="9"/>
-      <c r="F4" s="87"/>
-      <c r="H4" s="92"/>
-      <c r="I4" s="93" t="s">
+      <c r="F4" s="84"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="90" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="93" t="s">
+      <c r="J4" s="90" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="93"/>
-      <c r="L4" s="93"/>
-      <c r="M4" s="94"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="86" t="s">
+      <c r="K4" s="90"/>
+      <c r="L4" s="90"/>
+      <c r="M4" s="91"/>
+      <c r="O4" s="82"/>
+      <c r="P4" s="83" t="s">
         <v>41</v>
       </c>
-      <c r="Q4" s="86"/>
-      <c r="R4" s="86" t="s">
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="86"/>
-      <c r="T4" s="95"/>
-      <c r="U4" s="91"/>
-      <c r="V4" s="91"/>
-      <c r="W4" s="87"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="92"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="W4" s="84"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A5" s="84"/>
-      <c r="B5" s="96"/>
+      <c r="A5" s="176"/>
+      <c r="B5" s="93"/>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
-      <c r="F5" s="97"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="89" t="s">
+      <c r="F5" s="94"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="89" t="s">
+      <c r="J5" s="86" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="89"/>
-      <c r="L5" s="89"/>
-      <c r="M5" s="90"/>
+      <c r="K5" s="86"/>
+      <c r="L5" s="86"/>
+      <c r="M5" s="87"/>
       <c r="O5" s="8"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -3564,60 +3542,62 @@
       <c r="T5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="U5" s="91"/>
-      <c r="V5" s="91"/>
-      <c r="W5" s="87"/>
+      <c r="U5" s="88"/>
+      <c r="V5" s="88"/>
+      <c r="W5" s="84"/>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="98"/>
-      <c r="B6" s="98"/>
-      <c r="C6" s="99"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="99"/>
-      <c r="F6" s="100"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="99"/>
-      <c r="L6" s="99"/>
-      <c r="M6" s="100"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="99"/>
-      <c r="Q6" s="99"/>
-      <c r="R6" s="99"/>
-      <c r="S6" s="99"/>
-      <c r="T6" s="100"/>
-      <c r="U6" s="99"/>
-      <c r="V6" s="99"/>
-      <c r="W6" s="100"/>
+      <c r="A6" s="95"/>
+      <c r="B6" s="95"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="96"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="97"/>
+      <c r="H6" s="95"/>
+      <c r="I6" s="96"/>
+      <c r="J6" s="96"/>
+      <c r="K6" s="96"/>
+      <c r="L6" s="96"/>
+      <c r="M6" s="97"/>
+      <c r="O6" s="95"/>
+      <c r="P6" s="96"/>
+      <c r="Q6" s="96"/>
+      <c r="R6" s="96"/>
+      <c r="S6" s="96"/>
+      <c r="T6" s="97"/>
+      <c r="U6" s="96"/>
+      <c r="V6" s="96"/>
+      <c r="W6" s="97"/>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="101"/>
-      <c r="B7" s="85" t="s">
+      <c r="A7" s="203" t="s">
+        <v>437</v>
+      </c>
+      <c r="B7" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="86" t="s">
+      <c r="C7" s="83" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="103"/>
-      <c r="H7" s="85" t="s">
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="99"/>
+      <c r="H7" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="86" t="s">
+      <c r="I7" s="83" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="86" t="s">
+      <c r="J7" s="83" t="s">
         <v>51</v>
       </c>
-      <c r="K7" s="86" t="s">
+      <c r="K7" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="86" t="s">
+      <c r="L7" s="83" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="103"/>
+      <c r="M7" s="99"/>
       <c r="O7" s="8" t="s">
         <v>54</v>
       </c>
@@ -3636,78 +3616,76 @@
       <c r="T7" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="U7" s="102"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="104"/>
+      <c r="U7" s="98"/>
+      <c r="V7" s="98"/>
+      <c r="W7" s="100"/>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A8" s="105" t="s">
-        <v>437</v>
-      </c>
+    <row r="8" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="203"/>
       <c r="B8" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9"/>
-      <c r="D8" s="106"/>
-      <c r="E8" s="106"/>
-      <c r="F8" s="107"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="101"/>
+      <c r="F8" s="102"/>
       <c r="H8" s="8" t="s">
         <v>61</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="J8" s="108"/>
+      <c r="J8" s="103"/>
       <c r="K8" s="9" t="s">
         <v>63</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="M8" s="97"/>
-      <c r="O8" s="85" t="s">
+      <c r="M8" s="94"/>
+      <c r="O8" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="P8" s="86" t="s">
+      <c r="P8" s="83" t="s">
         <v>66</v>
       </c>
-      <c r="Q8" s="86" t="s">
+      <c r="Q8" s="83" t="s">
         <v>67</v>
       </c>
-      <c r="R8" s="86" t="s">
+      <c r="R8" s="83" t="s">
         <v>68</v>
       </c>
-      <c r="S8" s="86" t="s">
+      <c r="S8" s="83" t="s">
         <v>69</v>
       </c>
-      <c r="T8" s="95" t="s">
+      <c r="T8" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="U8" s="91"/>
-      <c r="V8" s="91"/>
-      <c r="W8" s="87"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="84"/>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A9" s="105"/>
-      <c r="B9" s="96"/>
-      <c r="C9" s="91"/>
+    <row r="9" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="203"/>
+      <c r="B9" s="93"/>
+      <c r="C9" s="88"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
-      <c r="F9" s="97"/>
-      <c r="H9" s="85" t="s">
+      <c r="F9" s="94"/>
+      <c r="H9" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="I9" s="86" t="s">
+      <c r="I9" s="83" t="s">
         <v>72</v>
       </c>
-      <c r="J9" s="108"/>
-      <c r="K9" s="86" t="s">
+      <c r="J9" s="103"/>
+      <c r="K9" s="83" t="s">
         <v>73</v>
       </c>
-      <c r="L9" s="86" t="s">
+      <c r="L9" s="83" t="s">
         <v>74</v>
       </c>
-      <c r="M9" s="107"/>
+      <c r="M9" s="102"/>
       <c r="O9" s="8" t="s">
         <v>75</v>
       </c>
@@ -3726,17 +3704,17 @@
       <c r="T9" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="U9" s="91"/>
-      <c r="V9" s="91"/>
-      <c r="W9" s="87"/>
+      <c r="U9" s="88"/>
+      <c r="V9" s="88"/>
+      <c r="W9" s="84"/>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A10" s="105"/>
-      <c r="B10" s="109"/>
-      <c r="C10" s="106"/>
-      <c r="D10" s="106"/>
-      <c r="E10" s="106"/>
-      <c r="F10" s="107"/>
+    <row r="10" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="203"/>
+      <c r="B10" s="104"/>
+      <c r="C10" s="101"/>
+      <c r="D10" s="101"/>
+      <c r="E10" s="101"/>
+      <c r="F10" s="102"/>
       <c r="H10" s="8"/>
       <c r="I10" s="9" t="s">
         <v>81</v>
@@ -3744,80 +3722,82 @@
       <c r="J10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
-      <c r="M10" s="87"/>
-      <c r="O10" s="109"/>
-      <c r="P10" s="106"/>
-      <c r="Q10" s="106"/>
-      <c r="R10" s="106"/>
-      <c r="S10" s="106"/>
-      <c r="T10" s="87"/>
+      <c r="M10" s="84"/>
+      <c r="O10" s="104"/>
+      <c r="P10" s="101"/>
+      <c r="Q10" s="101"/>
+      <c r="R10" s="101"/>
+      <c r="S10" s="101"/>
+      <c r="T10" s="84"/>
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
-      <c r="W10" s="97"/>
+      <c r="W10" s="94"/>
     </row>
-    <row r="11" spans="1:23" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="110"/>
-      <c r="B11" s="111"/>
+    <row r="11" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="204"/>
+      <c r="B11" s="105"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
-      <c r="F11" s="112"/>
-      <c r="H11" s="85"/>
+      <c r="F11" s="106"/>
+      <c r="H11" s="82"/>
       <c r="I11" s="14" t="s">
         <v>82</v>
       </c>
       <c r="J11" s="14"/>
       <c r="K11" s="14"/>
       <c r="L11" s="14"/>
-      <c r="M11" s="113"/>
-      <c r="O11" s="111"/>
+      <c r="M11" s="107"/>
+      <c r="O11" s="105"/>
       <c r="P11" s="13"/>
       <c r="Q11" s="13"/>
       <c r="R11" s="13"/>
       <c r="S11" s="13"/>
-      <c r="T11" s="113"/>
-      <c r="U11" s="114"/>
-      <c r="V11" s="114"/>
-      <c r="W11" s="115"/>
+      <c r="T11" s="107"/>
+      <c r="U11" s="108"/>
+      <c r="V11" s="108"/>
+      <c r="W11" s="109"/>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="98"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="99"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="99"/>
-      <c r="F12" s="100"/>
-      <c r="H12" s="98"/>
-      <c r="I12" s="99"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="99"/>
-      <c r="L12" s="99"/>
-      <c r="M12" s="100"/>
-      <c r="O12" s="98"/>
-      <c r="P12" s="99"/>
-      <c r="Q12" s="99"/>
-      <c r="R12" s="99"/>
-      <c r="S12" s="99"/>
-      <c r="T12" s="100"/>
-      <c r="U12" s="99"/>
-      <c r="V12" s="99"/>
-      <c r="W12" s="100"/>
+      <c r="A12" s="95"/>
+      <c r="B12" s="95"/>
+      <c r="C12" s="96"/>
+      <c r="D12" s="96"/>
+      <c r="E12" s="96"/>
+      <c r="F12" s="97"/>
+      <c r="H12" s="95"/>
+      <c r="I12" s="96"/>
+      <c r="J12" s="96"/>
+      <c r="K12" s="96"/>
+      <c r="L12" s="96"/>
+      <c r="M12" s="97"/>
+      <c r="O12" s="95"/>
+      <c r="P12" s="96"/>
+      <c r="Q12" s="96"/>
+      <c r="R12" s="96"/>
+      <c r="S12" s="96"/>
+      <c r="T12" s="97"/>
+      <c r="U12" s="96"/>
+      <c r="V12" s="96"/>
+      <c r="W12" s="97"/>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="116"/>
-      <c r="B13" s="85" t="s">
+      <c r="A13" s="170" t="s">
+        <v>438</v>
+      </c>
+      <c r="B13" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="86" t="s">
+      <c r="C13" s="83" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="86" t="s">
+      <c r="D13" s="83" t="s">
         <v>85</v>
       </c>
-      <c r="E13" s="86" t="s">
+      <c r="E13" s="83" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="95" t="s">
+      <c r="F13" s="92" t="s">
         <v>87</v>
       </c>
       <c r="H13" s="8" t="s">
@@ -3831,35 +3811,33 @@
       </c>
       <c r="K13" s="11"/>
       <c r="L13" s="11"/>
-      <c r="M13" s="87"/>
-      <c r="O13" s="85" t="s">
+      <c r="M13" s="84"/>
+      <c r="O13" s="82" t="s">
         <v>91</v>
       </c>
-      <c r="P13" s="86" t="s">
+      <c r="P13" s="83" t="s">
         <v>92</v>
       </c>
-      <c r="Q13" s="86" t="s">
+      <c r="Q13" s="83" t="s">
         <v>61</v>
       </c>
-      <c r="R13" s="86" t="s">
+      <c r="R13" s="83" t="s">
         <v>93</v>
       </c>
-      <c r="S13" s="86" t="s">
+      <c r="S13" s="83" t="s">
         <v>94</v>
       </c>
-      <c r="T13" s="95" t="s">
+      <c r="T13" s="92" t="s">
         <v>95</v>
       </c>
       <c r="U13" s="28" t="s">
         <v>96</v>
       </c>
       <c r="V13" s="28"/>
-      <c r="W13" s="117"/>
+      <c r="W13" s="110"/>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A14" s="116" t="s">
-        <v>438</v>
-      </c>
+    <row r="14" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="170"/>
       <c r="B14" s="8" t="s">
         <v>97</v>
       </c>
@@ -3875,18 +3853,18 @@
       <c r="F14" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="H14" s="85" t="s">
+      <c r="H14" s="82" t="s">
         <v>13</v>
       </c>
-      <c r="I14" s="86" t="s">
+      <c r="I14" s="83" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="86" t="s">
+      <c r="J14" s="83" t="s">
         <v>103</v>
       </c>
-      <c r="K14" s="102"/>
-      <c r="L14" s="102"/>
-      <c r="M14" s="103"/>
+      <c r="K14" s="98"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="99"/>
       <c r="O14" s="8" t="s">
         <v>93</v>
       </c>
@@ -3905,21 +3883,21 @@
       <c r="T14" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="U14" s="118" t="s">
+      <c r="U14" s="111" t="s">
         <v>109</v>
       </c>
-      <c r="V14" s="118"/>
-      <c r="W14" s="104"/>
+      <c r="V14" s="111"/>
+      <c r="W14" s="100"/>
     </row>
-    <row r="15" spans="1:23" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="119"/>
-      <c r="B15" s="120"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="121" t="s">
+    <row r="15" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="171"/>
+      <c r="B15" s="112"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="114"/>
       <c r="H15" s="16" t="s">
         <v>111</v>
       </c>
@@ -3927,38 +3905,41 @@
         <v>112</v>
       </c>
       <c r="J15" s="17"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="123"/>
-      <c r="M15" s="124"/>
-      <c r="O15" s="120" t="s">
+      <c r="K15" s="115"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="116"/>
+      <c r="O15" s="112" t="s">
         <v>113</v>
       </c>
-      <c r="P15" s="121" t="s">
+      <c r="P15" s="113" t="s">
         <v>114</v>
       </c>
-      <c r="Q15" s="121" t="s">
+      <c r="Q15" s="113" t="s">
         <v>115</v>
       </c>
-      <c r="R15" s="121" t="s">
+      <c r="R15" s="113" t="s">
         <v>116</v>
       </c>
-      <c r="S15" s="121" t="s">
+      <c r="S15" s="113" t="s">
         <v>117</v>
       </c>
-      <c r="T15" s="122"/>
+      <c r="T15" s="114"/>
       <c r="U15" s="37" t="s">
         <v>118</v>
       </c>
       <c r="V15" s="37"/>
-      <c r="W15" s="125"/>
+      <c r="W15" s="117"/>
     </row>
     <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="O1:T1"/>
     <mergeCell ref="U1:W1"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="A2:A5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3970,51 +3951,58 @@
   <dimension ref="A1:W13"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="18" width="8.88671875" style="126"/>
-    <col min="19" max="19" width="10.33203125" style="126" customWidth="1"/>
-    <col min="20" max="20" width="11.109375" style="126" customWidth="1"/>
-    <col min="21" max="16384" width="8.88671875" style="126"/>
+    <col min="1" max="1" width="6.44140625" style="118" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="8.88671875" style="118"/>
+    <col min="7" max="7" width="4.6640625" style="118" customWidth="1"/>
+    <col min="8" max="13" width="8.88671875" style="118"/>
+    <col min="14" max="14" width="5.5546875" style="118" customWidth="1"/>
+    <col min="15" max="18" width="8.88671875" style="118"/>
+    <col min="19" max="19" width="10.33203125" style="118" customWidth="1"/>
+    <col min="20" max="20" width="11.109375" style="118" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="118"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="144" t="s">
+      <c r="B1" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="145"/>
-      <c r="D1" s="145"/>
-      <c r="E1" s="145"/>
-      <c r="F1" s="146"/>
-      <c r="H1" s="144" t="s">
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="168"/>
+      <c r="H1" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="145"/>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="146"/>
-      <c r="O1" s="144" t="s">
+      <c r="I1" s="167"/>
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
+      <c r="L1" s="167"/>
+      <c r="M1" s="168"/>
+      <c r="O1" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="P1" s="145"/>
-      <c r="Q1" s="145"/>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="146"/>
-      <c r="U1" s="144" t="s">
+      <c r="P1" s="167"/>
+      <c r="Q1" s="167"/>
+      <c r="R1" s="167"/>
+      <c r="S1" s="167"/>
+      <c r="T1" s="168"/>
+      <c r="U1" s="166" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="145"/>
-      <c r="W1" s="146"/>
+      <c r="V1" s="167"/>
+      <c r="W1" s="168"/>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="127"/>
+      <c r="A2" s="200" t="s">
+        <v>436</v>
+      </c>
       <c r="B2" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="76"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="74"/>
       <c r="H2" s="20" t="s">
         <v>203</v>
       </c>
@@ -4037,18 +4025,16 @@
       <c r="P2" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="76"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="76"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="74"/>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A3" s="129" t="s">
-        <v>436</v>
-      </c>
+    <row r="3" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="201"/>
       <c r="B3" s="23" t="s">
         <v>210</v>
       </c>
@@ -4058,8 +4044,8 @@
       <c r="D3" s="14" t="s">
         <v>212</v>
       </c>
-      <c r="E3" s="91"/>
-      <c r="F3" s="87"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="84"/>
       <c r="H3" s="8" t="s">
         <v>213</v>
       </c>
@@ -4078,68 +4064,70 @@
       <c r="M3" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="O3" s="130"/>
-      <c r="P3" s="91"/>
-      <c r="Q3" s="91"/>
-      <c r="R3" s="91"/>
-      <c r="S3" s="91"/>
-      <c r="T3" s="87"/>
-      <c r="U3" s="91"/>
-      <c r="V3" s="91"/>
-      <c r="W3" s="87"/>
+      <c r="O3" s="120"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="84"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="W3" s="84"/>
     </row>
-    <row r="4" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="131"/>
+    <row r="4" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="202"/>
       <c r="B4" s="8" t="s">
         <v>219</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="D4" s="132"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="113"/>
-      <c r="H4" s="134"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="133"/>
-      <c r="M4" s="113"/>
-      <c r="O4" s="134"/>
-      <c r="P4" s="133"/>
-      <c r="Q4" s="133"/>
-      <c r="R4" s="133"/>
-      <c r="S4" s="133"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="91"/>
-      <c r="V4" s="91"/>
-      <c r="W4" s="87"/>
+      <c r="D4" s="121"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="107"/>
+      <c r="H4" s="123"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="107"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
+      <c r="T4" s="107"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="W4" s="84"/>
     </row>
     <row r="5" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="135"/>
-      <c r="B5" s="135"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="137"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="136"/>
-      <c r="M5" s="137"/>
-      <c r="O5" s="135"/>
-      <c r="P5" s="136"/>
-      <c r="Q5" s="136"/>
-      <c r="R5" s="136"/>
-      <c r="S5" s="136"/>
-      <c r="T5" s="137"/>
-      <c r="U5" s="136"/>
-      <c r="V5" s="136"/>
-      <c r="W5" s="137"/>
+      <c r="A5" s="124"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="125"/>
+      <c r="D5" s="125"/>
+      <c r="E5" s="125"/>
+      <c r="F5" s="126"/>
+      <c r="H5" s="124"/>
+      <c r="I5" s="125"/>
+      <c r="J5" s="125"/>
+      <c r="K5" s="125"/>
+      <c r="L5" s="125"/>
+      <c r="M5" s="126"/>
+      <c r="O5" s="124"/>
+      <c r="P5" s="125"/>
+      <c r="Q5" s="125"/>
+      <c r="R5" s="125"/>
+      <c r="S5" s="125"/>
+      <c r="T5" s="126"/>
+      <c r="U5" s="125"/>
+      <c r="V5" s="125"/>
+      <c r="W5" s="126"/>
     </row>
     <row r="6" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="73"/>
+      <c r="A6" s="178" t="s">
+        <v>437</v>
+      </c>
       <c r="B6" s="8" t="s">
         <v>221</v>
       </c>
@@ -4191,14 +4179,12 @@
       <c r="T6" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="U6" s="91"/>
-      <c r="V6" s="91"/>
-      <c r="W6" s="87"/>
+      <c r="U6" s="88"/>
+      <c r="V6" s="88"/>
+      <c r="W6" s="84"/>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A7" s="138" t="s">
-        <v>437</v>
-      </c>
+    <row r="7" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="179"/>
       <c r="B7" s="23" t="s">
         <v>238</v>
       </c>
@@ -4248,16 +4234,16 @@
       <c r="T7" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="U7" s="91"/>
-      <c r="V7" s="91"/>
-      <c r="W7" s="87"/>
+      <c r="U7" s="88"/>
+      <c r="V7" s="88"/>
+      <c r="W7" s="84"/>
     </row>
-    <row r="8" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="139"/>
+    <row r="8" spans="1:23" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="180"/>
       <c r="B8" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="C8" s="132"/>
+      <c r="C8" s="121"/>
       <c r="D8" s="9" t="s">
         <v>254</v>
       </c>
@@ -4287,7 +4273,7 @@
       <c r="P8" s="9" t="s">
         <v>262</v>
       </c>
-      <c r="Q8" s="132"/>
+      <c r="Q8" s="121"/>
       <c r="R8" s="9" t="s">
         <v>263</v>
       </c>
@@ -4297,35 +4283,37 @@
       <c r="T8" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="U8" s="91"/>
-      <c r="V8" s="91"/>
-      <c r="W8" s="87"/>
+      <c r="U8" s="88"/>
+      <c r="V8" s="88"/>
+      <c r="W8" s="84"/>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="135"/>
-      <c r="B9" s="135"/>
-      <c r="C9" s="136"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="136"/>
-      <c r="F9" s="137"/>
-      <c r="H9" s="135"/>
-      <c r="I9" s="136"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="136"/>
-      <c r="L9" s="136"/>
-      <c r="M9" s="137"/>
-      <c r="O9" s="135"/>
-      <c r="P9" s="136"/>
-      <c r="Q9" s="136"/>
-      <c r="R9" s="136"/>
-      <c r="S9" s="136"/>
-      <c r="T9" s="137"/>
-      <c r="U9" s="136"/>
-      <c r="V9" s="136"/>
-      <c r="W9" s="137"/>
+      <c r="A9" s="124"/>
+      <c r="B9" s="124"/>
+      <c r="C9" s="125"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="125"/>
+      <c r="F9" s="126"/>
+      <c r="H9" s="124"/>
+      <c r="I9" s="125"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="125"/>
+      <c r="L9" s="125"/>
+      <c r="M9" s="126"/>
+      <c r="O9" s="124"/>
+      <c r="P9" s="125"/>
+      <c r="Q9" s="125"/>
+      <c r="R9" s="125"/>
+      <c r="S9" s="125"/>
+      <c r="T9" s="126"/>
+      <c r="U9" s="125"/>
+      <c r="V9" s="125"/>
+      <c r="W9" s="126"/>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="140"/>
+      <c r="A10" s="169" t="s">
+        <v>438</v>
+      </c>
       <c r="B10" s="23" t="s">
         <v>266</v>
       </c>
@@ -4354,7 +4342,7 @@
         <v>274</v>
       </c>
       <c r="L10" s="11"/>
-      <c r="M10" s="87"/>
+      <c r="M10" s="84"/>
       <c r="O10" s="23" t="s">
         <v>275</v>
       </c>
@@ -4370,17 +4358,15 @@
       <c r="S10" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="T10" s="87"/>
+      <c r="T10" s="84"/>
       <c r="U10" s="28"/>
       <c r="V10" s="4" t="s">
         <v>280</v>
       </c>
       <c r="W10" s="29"/>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A11" s="116" t="s">
-        <v>438</v>
-      </c>
+    <row r="11" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="170"/>
       <c r="B11" s="8" t="s">
         <v>281</v>
       </c>
@@ -4406,8 +4392,8 @@
         <v>286</v>
       </c>
       <c r="K11" s="14"/>
-      <c r="L11" s="106"/>
-      <c r="M11" s="87"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="84"/>
       <c r="O11" s="8" t="s">
         <v>287</v>
       </c>
@@ -4423,15 +4409,15 @@
       <c r="S11" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="T11" s="87"/>
+      <c r="T11" s="84"/>
       <c r="U11" s="30"/>
       <c r="V11" s="14" t="s">
         <v>291</v>
       </c>
       <c r="W11" s="31"/>
     </row>
-    <row r="12" spans="1:23" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="141"/>
+    <row r="12" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="171"/>
       <c r="B12" s="32" t="s">
         <v>292</v>
       </c>
@@ -4450,9 +4436,9 @@
       <c r="J12" s="17"/>
       <c r="K12" s="17"/>
       <c r="L12" s="13"/>
-      <c r="M12" s="113"/>
-      <c r="O12" s="142"/>
-      <c r="P12" s="143"/>
+      <c r="M12" s="107"/>
+      <c r="O12" s="127"/>
+      <c r="P12" s="128"/>
       <c r="Q12" s="33"/>
       <c r="R12" s="33" t="s">
         <v>296</v>
@@ -4460,7 +4446,7 @@
       <c r="S12" s="33" t="s">
         <v>297</v>
       </c>
-      <c r="T12" s="113"/>
+      <c r="T12" s="107"/>
       <c r="U12" s="37" t="s">
         <v>298</v>
       </c>
@@ -4471,11 +4457,14 @@
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
     <mergeCell ref="H1:M1"/>
     <mergeCell ref="O1:T1"/>
     <mergeCell ref="U1:W1"/>
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A2:A4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4486,574 +4475,603 @@
   <dimension ref="A1:W12"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="169"/>
+    <col min="1" max="1" width="6.44140625" style="130" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="8.88671875" style="130"/>
+    <col min="8" max="8" width="4" style="130" customWidth="1"/>
+    <col min="9" max="15" width="8.88671875" style="130"/>
+    <col min="16" max="16" width="4.109375" style="130" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="130"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="165"/>
-      <c r="B1" s="166" t="s">
+      <c r="A1" s="129"/>
+      <c r="B1" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="167"/>
-      <c r="D1" s="167"/>
-      <c r="E1" s="167"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="168"/>
-      <c r="I1" s="144" t="s">
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="174"/>
+      <c r="H1" s="199"/>
+      <c r="I1" s="166" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="145"/>
-      <c r="K1" s="145"/>
-      <c r="L1" s="145"/>
-      <c r="M1" s="145"/>
-      <c r="N1" s="145"/>
-      <c r="O1" s="146"/>
-      <c r="Q1" s="144" t="s">
+      <c r="J1" s="167"/>
+      <c r="K1" s="167"/>
+      <c r="L1" s="167"/>
+      <c r="M1" s="167"/>
+      <c r="N1" s="167"/>
+      <c r="O1" s="168"/>
+      <c r="P1" s="199"/>
+      <c r="Q1" s="166" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="145"/>
-      <c r="S1" s="145"/>
-      <c r="T1" s="145"/>
-      <c r="U1" s="145"/>
-      <c r="V1" s="146"/>
-      <c r="W1" s="170" t="s">
+      <c r="R1" s="167"/>
+      <c r="S1" s="167"/>
+      <c r="T1" s="167"/>
+      <c r="U1" s="167"/>
+      <c r="V1" s="168"/>
+      <c r="W1" s="131" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="171" t="s">
+      <c r="A2" s="175" t="s">
         <v>436</v>
       </c>
-      <c r="B2" s="172" t="s">
+      <c r="B2" s="132" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="173" t="s">
+      <c r="C2" s="133" t="s">
         <v>205</v>
       </c>
-      <c r="D2" s="173" t="s">
+      <c r="D2" s="133" t="s">
         <v>301</v>
       </c>
-      <c r="E2" s="173" t="s">
+      <c r="E2" s="133" t="s">
         <v>302</v>
       </c>
-      <c r="F2" s="173" t="s">
+      <c r="F2" s="133" t="s">
         <v>303</v>
       </c>
-      <c r="G2" s="174"/>
-      <c r="I2" s="172" t="s">
+      <c r="G2" s="134"/>
+      <c r="H2" s="199"/>
+      <c r="I2" s="132" t="s">
         <v>345</v>
       </c>
-      <c r="J2" s="173" t="s">
+      <c r="J2" s="133" t="s">
         <v>346</v>
       </c>
-      <c r="K2" s="173" t="s">
+      <c r="K2" s="133" t="s">
         <v>347</v>
       </c>
-      <c r="L2" s="175"/>
-      <c r="M2" s="175"/>
-      <c r="N2" s="175"/>
-      <c r="O2" s="174"/>
-      <c r="Q2" s="172" t="s">
+      <c r="L2" s="135"/>
+      <c r="M2" s="135"/>
+      <c r="N2" s="135"/>
+      <c r="O2" s="134"/>
+      <c r="P2" s="199"/>
+      <c r="Q2" s="132" t="s">
         <v>385</v>
       </c>
-      <c r="R2" s="173" t="s">
+      <c r="R2" s="133" t="s">
         <v>386</v>
       </c>
-      <c r="S2" s="173" t="s">
+      <c r="S2" s="133" t="s">
         <v>304</v>
       </c>
-      <c r="T2" s="173" t="s">
+      <c r="T2" s="133" t="s">
         <v>387</v>
       </c>
-      <c r="U2" s="176"/>
-      <c r="V2" s="177" t="s">
+      <c r="U2" s="136"/>
+      <c r="V2" s="137" t="s">
         <v>388</v>
       </c>
-      <c r="W2" s="178"/>
+      <c r="W2" s="138"/>
     </row>
     <row r="3" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="179"/>
-      <c r="B3" s="180" t="s">
+      <c r="A3" s="176"/>
+      <c r="B3" s="139" t="s">
         <v>304</v>
       </c>
-      <c r="C3" s="181" t="s">
+      <c r="C3" s="140" t="s">
         <v>305</v>
       </c>
-      <c r="D3" s="181" t="s">
+      <c r="D3" s="140" t="s">
         <v>306</v>
       </c>
-      <c r="E3" s="181" t="s">
+      <c r="E3" s="140" t="s">
         <v>307</v>
       </c>
-      <c r="F3" s="181" t="s">
+      <c r="F3" s="140" t="s">
         <v>308</v>
       </c>
-      <c r="G3" s="182"/>
-      <c r="I3" s="180" t="s">
+      <c r="G3" s="141"/>
+      <c r="H3" s="199"/>
+      <c r="I3" s="139" t="s">
         <v>348</v>
       </c>
-      <c r="J3" s="181" t="s">
+      <c r="J3" s="140" t="s">
         <v>349</v>
       </c>
-      <c r="K3" s="181" t="s">
+      <c r="K3" s="140" t="s">
         <v>350</v>
       </c>
-      <c r="L3" s="183"/>
-      <c r="M3" s="183"/>
-      <c r="N3" s="165"/>
-      <c r="O3" s="184"/>
-      <c r="Q3" s="180" t="s">
+      <c r="L3" s="142"/>
+      <c r="M3" s="142"/>
+      <c r="N3" s="129"/>
+      <c r="O3" s="143"/>
+      <c r="P3" s="199"/>
+      <c r="Q3" s="139" t="s">
         <v>389</v>
       </c>
-      <c r="R3" s="181" t="s">
+      <c r="R3" s="140" t="s">
         <v>390</v>
       </c>
-      <c r="S3" s="181" t="s">
+      <c r="S3" s="140" t="s">
         <v>391</v>
       </c>
-      <c r="T3" s="181" t="s">
+      <c r="T3" s="140" t="s">
         <v>392</v>
       </c>
-      <c r="U3" s="181" t="s">
+      <c r="U3" s="140" t="s">
         <v>393</v>
       </c>
-      <c r="V3" s="185" t="s">
+      <c r="V3" s="144" t="s">
         <v>394</v>
       </c>
-      <c r="W3" s="184"/>
+      <c r="W3" s="143"/>
     </row>
     <row r="4" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="186"/>
-      <c r="B4" s="187" t="s">
+      <c r="A4" s="177"/>
+      <c r="B4" s="145" t="s">
         <v>309</v>
       </c>
-      <c r="C4" s="188"/>
-      <c r="D4" s="189" t="s">
+      <c r="C4" s="146"/>
+      <c r="D4" s="147" t="s">
         <v>310</v>
       </c>
-      <c r="E4" s="189" t="s">
+      <c r="E4" s="147" t="s">
         <v>311</v>
       </c>
-      <c r="F4" s="188"/>
-      <c r="G4" s="190"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="192"/>
-      <c r="K4" s="192"/>
-      <c r="L4" s="192"/>
-      <c r="M4" s="192"/>
-      <c r="N4" s="192"/>
-      <c r="O4" s="190"/>
-      <c r="Q4" s="191"/>
-      <c r="R4" s="192"/>
-      <c r="S4" s="192"/>
-      <c r="T4" s="192"/>
-      <c r="U4" s="192"/>
-      <c r="V4" s="190"/>
-      <c r="W4" s="190"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="199"/>
+      <c r="I4" s="149"/>
+      <c r="J4" s="150"/>
+      <c r="K4" s="150"/>
+      <c r="L4" s="150"/>
+      <c r="M4" s="150"/>
+      <c r="N4" s="150"/>
+      <c r="O4" s="148"/>
+      <c r="P4" s="199"/>
+      <c r="Q4" s="149"/>
+      <c r="R4" s="150"/>
+      <c r="S4" s="150"/>
+      <c r="T4" s="150"/>
+      <c r="U4" s="150"/>
+      <c r="V4" s="148"/>
+      <c r="W4" s="148"/>
     </row>
     <row r="5" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="193"/>
-      <c r="B5" s="193"/>
-      <c r="C5" s="193"/>
-      <c r="D5" s="193"/>
-      <c r="E5" s="193"/>
-      <c r="F5" s="193"/>
-      <c r="G5" s="193"/>
-      <c r="I5" s="193"/>
-      <c r="J5" s="193"/>
-      <c r="K5" s="193"/>
-      <c r="L5" s="193"/>
-      <c r="M5" s="193"/>
-      <c r="N5" s="193"/>
-      <c r="O5" s="193"/>
-      <c r="Q5" s="193"/>
-      <c r="R5" s="193"/>
-      <c r="S5" s="193"/>
-      <c r="T5" s="193"/>
-      <c r="U5" s="193"/>
-      <c r="V5" s="193"/>
-      <c r="W5" s="193"/>
+      <c r="A5" s="151"/>
+      <c r="B5" s="151"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
+      <c r="H5" s="199"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="151"/>
+      <c r="L5" s="151"/>
+      <c r="M5" s="151"/>
+      <c r="N5" s="151"/>
+      <c r="O5" s="151"/>
+      <c r="P5" s="199"/>
+      <c r="Q5" s="151"/>
+      <c r="R5" s="151"/>
+      <c r="S5" s="151"/>
+      <c r="T5" s="151"/>
+      <c r="U5" s="151"/>
+      <c r="V5" s="151"/>
+      <c r="W5" s="151"/>
     </row>
     <row r="6" spans="1:23" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="194" t="s">
+      <c r="A6" s="178" t="s">
         <v>437</v>
       </c>
-      <c r="B6" s="172" t="s">
+      <c r="B6" s="132" t="s">
         <v>431</v>
       </c>
-      <c r="C6" s="173" t="s">
+      <c r="C6" s="133" t="s">
         <v>313</v>
       </c>
-      <c r="D6" s="173" t="s">
+      <c r="D6" s="133" t="s">
         <v>314</v>
       </c>
-      <c r="E6" s="173" t="s">
+      <c r="E6" s="133" t="s">
         <v>315</v>
       </c>
-      <c r="F6" s="173" t="s">
+      <c r="F6" s="133" t="s">
         <v>316</v>
       </c>
-      <c r="G6" s="177" t="s">
+      <c r="G6" s="137" t="s">
         <v>317</v>
       </c>
-      <c r="I6" s="172" t="s">
+      <c r="H6" s="199"/>
+      <c r="I6" s="132" t="s">
         <v>351</v>
       </c>
-      <c r="J6" s="173" t="s">
+      <c r="J6" s="133" t="s">
         <v>352</v>
       </c>
-      <c r="K6" s="173" t="s">
+      <c r="K6" s="133" t="s">
         <v>353</v>
       </c>
-      <c r="L6" s="173" t="s">
+      <c r="L6" s="133" t="s">
         <v>354</v>
       </c>
-      <c r="M6" s="173" t="s">
+      <c r="M6" s="133" t="s">
         <v>312</v>
       </c>
-      <c r="N6" s="173" t="s">
+      <c r="N6" s="133" t="s">
         <v>355</v>
       </c>
-      <c r="O6" s="195"/>
-      <c r="Q6" s="172" t="s">
+      <c r="O6" s="152"/>
+      <c r="P6" s="199"/>
+      <c r="Q6" s="132" t="s">
         <v>395</v>
       </c>
-      <c r="R6" s="173" t="s">
+      <c r="R6" s="133" t="s">
         <v>396</v>
       </c>
-      <c r="S6" s="173" t="s">
+      <c r="S6" s="133" t="s">
         <v>397</v>
       </c>
-      <c r="T6" s="173" t="s">
+      <c r="T6" s="133" t="s">
         <v>398</v>
       </c>
-      <c r="U6" s="173" t="s">
+      <c r="U6" s="133" t="s">
         <v>399</v>
       </c>
-      <c r="V6" s="177" t="s">
+      <c r="V6" s="137" t="s">
         <v>400</v>
       </c>
-      <c r="W6" s="196"/>
+      <c r="W6" s="153"/>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="197"/>
-      <c r="B7" s="180" t="s">
+      <c r="A7" s="179"/>
+      <c r="B7" s="139" t="s">
         <v>318</v>
       </c>
-      <c r="C7" s="181" t="s">
+      <c r="C7" s="140" t="s">
         <v>319</v>
       </c>
-      <c r="D7" s="181" t="s">
+      <c r="D7" s="140" t="s">
         <v>320</v>
       </c>
-      <c r="E7" s="181" t="s">
+      <c r="E7" s="140" t="s">
         <v>321</v>
       </c>
-      <c r="F7" s="181" t="s">
+      <c r="F7" s="140" t="s">
         <v>322</v>
       </c>
-      <c r="G7" s="185" t="s">
+      <c r="G7" s="144" t="s">
         <v>323</v>
       </c>
-      <c r="I7" s="180" t="s">
+      <c r="H7" s="199"/>
+      <c r="I7" s="139" t="s">
         <v>356</v>
       </c>
-      <c r="J7" s="181" t="s">
+      <c r="J7" s="140" t="s">
         <v>357</v>
       </c>
-      <c r="K7" s="181" t="s">
+      <c r="K7" s="140" t="s">
         <v>358</v>
       </c>
-      <c r="L7" s="181" t="s">
+      <c r="L7" s="140" t="s">
         <v>359</v>
       </c>
-      <c r="M7" s="181" t="s">
+      <c r="M7" s="140" t="s">
         <v>360</v>
       </c>
-      <c r="N7" s="181" t="s">
+      <c r="N7" s="140" t="s">
         <v>361</v>
       </c>
-      <c r="O7" s="198"/>
-      <c r="Q7" s="180" t="s">
+      <c r="O7" s="154"/>
+      <c r="P7" s="199"/>
+      <c r="Q7" s="139" t="s">
         <v>401</v>
       </c>
-      <c r="R7" s="181" t="s">
+      <c r="R7" s="140" t="s">
         <v>402</v>
       </c>
-      <c r="S7" s="181" t="s">
+      <c r="S7" s="140" t="s">
         <v>403</v>
       </c>
-      <c r="T7" s="181" t="s">
+      <c r="T7" s="140" t="s">
         <v>404</v>
       </c>
-      <c r="U7" s="181" t="s">
+      <c r="U7" s="140" t="s">
         <v>405</v>
       </c>
-      <c r="V7" s="185" t="s">
+      <c r="V7" s="144" t="s">
         <v>406</v>
       </c>
-      <c r="W7" s="199"/>
+      <c r="W7" s="155"/>
     </row>
     <row r="8" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="200"/>
-      <c r="B8" s="187" t="s">
+      <c r="A8" s="180"/>
+      <c r="B8" s="145" t="s">
         <v>324</v>
       </c>
-      <c r="C8" s="189" t="s">
+      <c r="C8" s="147" t="s">
         <v>325</v>
       </c>
-      <c r="D8" s="189" t="s">
+      <c r="D8" s="147" t="s">
         <v>326</v>
       </c>
-      <c r="E8" s="189" t="s">
+      <c r="E8" s="147" t="s">
         <v>327</v>
       </c>
-      <c r="F8" s="189" t="s">
+      <c r="F8" s="147" t="s">
         <v>328</v>
       </c>
-      <c r="G8" s="201" t="s">
+      <c r="G8" s="156" t="s">
         <v>329</v>
       </c>
-      <c r="I8" s="187" t="s">
+      <c r="H8" s="199"/>
+      <c r="I8" s="145" t="s">
         <v>362</v>
       </c>
-      <c r="J8" s="189" t="s">
+      <c r="J8" s="147" t="s">
         <v>363</v>
       </c>
-      <c r="K8" s="189" t="s">
+      <c r="K8" s="147" t="s">
         <v>364</v>
       </c>
-      <c r="L8" s="189" t="s">
+      <c r="L8" s="147" t="s">
         <v>365</v>
       </c>
-      <c r="M8" s="189" t="s">
+      <c r="M8" s="147" t="s">
         <v>366</v>
       </c>
-      <c r="N8" s="189" t="s">
+      <c r="N8" s="147" t="s">
         <v>367</v>
       </c>
-      <c r="O8" s="202"/>
-      <c r="Q8" s="187" t="s">
+      <c r="O8" s="157"/>
+      <c r="P8" s="199"/>
+      <c r="Q8" s="145" t="s">
         <v>407</v>
       </c>
-      <c r="R8" s="189" t="s">
+      <c r="R8" s="147" t="s">
         <v>408</v>
       </c>
-      <c r="S8" s="189" t="s">
+      <c r="S8" s="147" t="s">
         <v>409</v>
       </c>
-      <c r="T8" s="189" t="s">
+      <c r="T8" s="147" t="s">
         <v>410</v>
       </c>
-      <c r="U8" s="189" t="s">
+      <c r="U8" s="147" t="s">
         <v>411</v>
       </c>
-      <c r="V8" s="201" t="s">
+      <c r="V8" s="156" t="s">
         <v>412</v>
       </c>
-      <c r="W8" s="203"/>
+      <c r="W8" s="158"/>
     </row>
     <row r="9" spans="1:23" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="204"/>
-      <c r="B9" s="204"/>
-      <c r="C9" s="204"/>
-      <c r="D9" s="204"/>
-      <c r="E9" s="204"/>
-      <c r="F9" s="204"/>
-      <c r="G9" s="204"/>
-      <c r="I9" s="204"/>
-      <c r="J9" s="204"/>
-      <c r="K9" s="204"/>
-      <c r="L9" s="204"/>
-      <c r="M9" s="204"/>
-      <c r="N9" s="204"/>
-      <c r="O9" s="204"/>
-      <c r="Q9" s="204"/>
-      <c r="R9" s="204"/>
-      <c r="S9" s="204"/>
-      <c r="T9" s="204"/>
-      <c r="U9" s="204"/>
-      <c r="V9" s="204"/>
-      <c r="W9" s="204"/>
+      <c r="A9" s="159"/>
+      <c r="B9" s="159"/>
+      <c r="C9" s="159"/>
+      <c r="D9" s="159"/>
+      <c r="E9" s="159"/>
+      <c r="F9" s="159"/>
+      <c r="G9" s="159"/>
+      <c r="H9" s="199"/>
+      <c r="I9" s="159"/>
+      <c r="J9" s="159"/>
+      <c r="K9" s="159"/>
+      <c r="L9" s="159"/>
+      <c r="M9" s="159"/>
+      <c r="N9" s="159"/>
+      <c r="O9" s="159"/>
+      <c r="P9" s="199"/>
+      <c r="Q9" s="159"/>
+      <c r="R9" s="159"/>
+      <c r="S9" s="159"/>
+      <c r="T9" s="159"/>
+      <c r="U9" s="159"/>
+      <c r="V9" s="159"/>
+      <c r="W9" s="159"/>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="205" t="s">
+      <c r="A10" s="169" t="s">
         <v>438</v>
       </c>
-      <c r="B10" s="206" t="s">
+      <c r="B10" s="160" t="s">
         <v>330</v>
       </c>
-      <c r="C10" s="207" t="s">
+      <c r="C10" s="161" t="s">
         <v>331</v>
       </c>
-      <c r="D10" s="207" t="s">
+      <c r="D10" s="161" t="s">
         <v>433</v>
       </c>
-      <c r="E10" s="207" t="s">
+      <c r="E10" s="161" t="s">
         <v>332</v>
       </c>
-      <c r="F10" s="207" t="s">
+      <c r="F10" s="161" t="s">
         <v>333</v>
       </c>
-      <c r="G10" s="208" t="s">
+      <c r="G10" s="162" t="s">
         <v>334</v>
       </c>
-      <c r="I10" s="206" t="s">
+      <c r="H10" s="199"/>
+      <c r="I10" s="160" t="s">
         <v>368</v>
       </c>
-      <c r="J10" s="207" t="s">
+      <c r="J10" s="161" t="s">
         <v>369</v>
       </c>
-      <c r="K10" s="207" t="s">
+      <c r="K10" s="161" t="s">
         <v>370</v>
       </c>
-      <c r="L10" s="207" t="s">
+      <c r="L10" s="161" t="s">
         <v>371</v>
       </c>
-      <c r="M10" s="207" t="s">
+      <c r="M10" s="161" t="s">
         <v>372</v>
       </c>
-      <c r="N10" s="207" t="s">
+      <c r="N10" s="161" t="s">
         <v>373</v>
       </c>
-      <c r="O10" s="209"/>
-      <c r="Q10" s="206" t="s">
+      <c r="O10" s="163"/>
+      <c r="P10" s="199"/>
+      <c r="Q10" s="160" t="s">
         <v>413</v>
       </c>
-      <c r="R10" s="207" t="s">
+      <c r="R10" s="161" t="s">
         <v>414</v>
       </c>
-      <c r="S10" s="207" t="s">
+      <c r="S10" s="161" t="s">
         <v>415</v>
       </c>
-      <c r="T10" s="207" t="s">
+      <c r="T10" s="161" t="s">
         <v>416</v>
       </c>
-      <c r="U10" s="207" t="s">
+      <c r="U10" s="161" t="s">
         <v>417</v>
       </c>
-      <c r="V10" s="208" t="s">
+      <c r="V10" s="162" t="s">
         <v>418</v>
       </c>
-      <c r="W10" s="210" t="s">
+      <c r="W10" s="164" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="211"/>
-      <c r="B11" s="180" t="s">
+      <c r="A11" s="170"/>
+      <c r="B11" s="139" t="s">
         <v>432</v>
       </c>
-      <c r="C11" s="181" t="s">
+      <c r="C11" s="140" t="s">
         <v>335</v>
       </c>
-      <c r="D11" s="181" t="s">
+      <c r="D11" s="140" t="s">
         <v>336</v>
       </c>
-      <c r="E11" s="181" t="s">
+      <c r="E11" s="140" t="s">
         <v>337</v>
       </c>
-      <c r="F11" s="181" t="s">
+      <c r="F11" s="140" t="s">
         <v>338</v>
       </c>
-      <c r="G11" s="185" t="s">
+      <c r="G11" s="144" t="s">
         <v>339</v>
       </c>
-      <c r="I11" s="180" t="s">
+      <c r="H11" s="199"/>
+      <c r="I11" s="139" t="s">
         <v>374</v>
       </c>
-      <c r="J11" s="181" t="s">
+      <c r="J11" s="140" t="s">
         <v>375</v>
       </c>
-      <c r="K11" s="181" t="s">
+      <c r="K11" s="140" t="s">
         <v>376</v>
       </c>
-      <c r="L11" s="181" t="s">
+      <c r="L11" s="140" t="s">
         <v>377</v>
       </c>
-      <c r="M11" s="181" t="s">
+      <c r="M11" s="140" t="s">
         <v>378</v>
       </c>
-      <c r="N11" s="181" t="s">
+      <c r="N11" s="140" t="s">
         <v>379</v>
       </c>
-      <c r="O11" s="182"/>
-      <c r="Q11" s="180" t="s">
+      <c r="O11" s="141"/>
+      <c r="P11" s="199"/>
+      <c r="Q11" s="139" t="s">
         <v>419</v>
       </c>
-      <c r="R11" s="181" t="s">
+      <c r="R11" s="140" t="s">
         <v>420</v>
       </c>
-      <c r="S11" s="181" t="s">
+      <c r="S11" s="140" t="s">
         <v>421</v>
       </c>
-      <c r="T11" s="181" t="s">
+      <c r="T11" s="140" t="s">
         <v>422</v>
       </c>
-      <c r="U11" s="181" t="s">
+      <c r="U11" s="140" t="s">
         <v>435</v>
       </c>
-      <c r="V11" s="185" t="s">
+      <c r="V11" s="144" t="s">
         <v>423</v>
       </c>
-      <c r="W11" s="210" t="s">
+      <c r="W11" s="164" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="212"/>
-      <c r="B12" s="187" t="s">
+      <c r="A12" s="171"/>
+      <c r="B12" s="145" t="s">
         <v>340</v>
       </c>
-      <c r="C12" s="189" t="s">
+      <c r="C12" s="147" t="s">
         <v>341</v>
       </c>
-      <c r="D12" s="189" t="s">
+      <c r="D12" s="147" t="s">
         <v>342</v>
       </c>
-      <c r="E12" s="188"/>
-      <c r="F12" s="189" t="s">
+      <c r="E12" s="146"/>
+      <c r="F12" s="147" t="s">
         <v>343</v>
       </c>
-      <c r="G12" s="201" t="s">
+      <c r="G12" s="156" t="s">
         <v>344</v>
       </c>
-      <c r="I12" s="187" t="s">
+      <c r="H12" s="199"/>
+      <c r="I12" s="145" t="s">
         <v>380</v>
       </c>
-      <c r="J12" s="189" t="s">
+      <c r="J12" s="147" t="s">
         <v>381</v>
       </c>
-      <c r="K12" s="189" t="s">
+      <c r="K12" s="147" t="s">
         <v>382</v>
       </c>
-      <c r="L12" s="189" t="s">
+      <c r="L12" s="147" t="s">
         <v>377</v>
       </c>
-      <c r="M12" s="189" t="s">
+      <c r="M12" s="147" t="s">
         <v>383</v>
       </c>
-      <c r="N12" s="189" t="s">
+      <c r="N12" s="147" t="s">
         <v>384</v>
       </c>
-      <c r="O12" s="190"/>
-      <c r="Q12" s="187" t="s">
+      <c r="O12" s="148"/>
+      <c r="P12" s="199"/>
+      <c r="Q12" s="145" t="s">
         <v>424</v>
       </c>
-      <c r="R12" s="189" t="s">
+      <c r="R12" s="147" t="s">
         <v>425</v>
       </c>
-      <c r="S12" s="188"/>
-      <c r="T12" s="189" t="s">
+      <c r="S12" s="146"/>
+      <c r="T12" s="147" t="s">
         <v>426</v>
       </c>
-      <c r="U12" s="189" t="s">
+      <c r="U12" s="147" t="s">
         <v>427</v>
       </c>
-      <c r="V12" s="201" t="s">
+      <c r="V12" s="156" t="s">
         <v>428</v>
       </c>
-      <c r="W12" s="213" t="s">
+      <c r="W12" s="165" t="s">
         <v>430</v>
       </c>
     </row>
